--- a/src/docs/excel_templates/employee_profile.xlsx
+++ b/src/docs/excel_templates/employee_profile.xlsx
@@ -27,10 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
-  <si>
-    <t>Template Columns</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Employee Code</t>
   </si>
@@ -1085,108 +1082,141 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="4"/>
+  <dimension ref="A1:AE4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="3"/>
+  <cols>
+    <col min="1" max="1" width="16.2" customWidth="1"/>
+    <col min="2" max="2" width="5.3" customWidth="1"/>
+    <col min="3" max="3" width="11.2" customWidth="1"/>
+    <col min="4" max="4" width="13.3" customWidth="1"/>
+    <col min="5" max="6" width="10.9" customWidth="1"/>
+    <col min="7" max="7" width="6.8" customWidth="1"/>
+    <col min="8" max="8" width="12.2" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="15.9" customWidth="1"/>
+    <col min="11" max="11" width="17.2" customWidth="1"/>
+    <col min="12" max="12" width="13.9" customWidth="1"/>
+    <col min="13" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12.5" customWidth="1"/>
+    <col min="15" max="15" width="13.2" customWidth="1"/>
+    <col min="16" max="16" width="13.7" customWidth="1"/>
+    <col min="17" max="17" width="8" customWidth="1"/>
+    <col min="18" max="18" width="8.7" customWidth="1"/>
+    <col min="19" max="19" width="12.7" customWidth="1"/>
+    <col min="20" max="20" width="15.2" customWidth="1"/>
+    <col min="21" max="21" width="20.6" customWidth="1"/>
+    <col min="22" max="22" width="8" customWidth="1"/>
+    <col min="23" max="23" width="13.4" customWidth="1"/>
+    <col min="24" max="24" width="7.1" customWidth="1"/>
+    <col min="25" max="25" width="8.3" customWidth="1"/>
+    <col min="26" max="26" width="8.8" customWidth="1"/>
+    <col min="27" max="27" width="8.5" customWidth="1"/>
+    <col min="28" max="28" width="5.5" customWidth="1"/>
+    <col min="29" max="29" width="7.7" customWidth="1"/>
+    <col min="30" max="30" width="10.9" customWidth="1"/>
+    <col min="31" max="31" width="6.4" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:1">
+    <row r="1" s="1" customFormat="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:31">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>31</v>
-      </c>
+    <row r="2" spans="19:23">
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="W2" s="3"/>
     </row>
     <row r="3" spans="19:23">
       <c r="S3" s="2"/>
@@ -1200,16 +1230,7 @@
       <c r="U4" s="2"/>
       <c r="W4" s="3"/>
     </row>
-    <row r="5" spans="19:23">
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-      <c r="W5" s="3"/>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="W4:W5" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
